--- a/datasets/tenant-inputs/generated/harbortrust-bank/standard-2026-07-v3/core-dimensions/02_org_ownership.xlsx
+++ b/datasets/tenant-inputs/generated/harbortrust-bank/standard-2026-07-v3/core-dimensions/02_org_ownership.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="R3b201f3b0a654b42"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client Intake" sheetId="2" r:id="Re82c0cf551724be7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questionnaire" sheetId="3" r:id="R3bbfbb910cd542c7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Examples" sheetId="4" r:id="R2995fb3fa6ae4135"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference Values" sheetId="5" r:id="R5e2a28463af34a1d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationship Expectations" sheetId="6" r:id="Rf8d7bee8a797422a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="Rd9018a6f0c2c4ab4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client Intake" sheetId="2" r:id="R116d35f71dfd46ea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questionnaire" sheetId="3" r:id="R6335f40a4e954bfc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Examples" sheetId="4" r:id="Rcc54653aa4c54566"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference Values" sheetId="5" r:id="R0be0b57126384430"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationship Expectations" sheetId="6" r:id="R45d836024c7348e0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -624,7 +624,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R122a5bc93b1d4c27"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9273fa6e0fcb4bf7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -785,7 +785,7 @@
         <x:v>Executive Office SME lead; data steward; technology owner</x:v>
       </x:c>
       <x:c r="M6" s="78" t="str">
-        <x:v>Named people and approval thresholds require client confirmation.</x:v>
+        <x:v>Validate Corporate strategy office (record 1) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for org ownership.</x:v>
       </x:c>
       <x:c r="N6" s="41" t="str">
         <x:v>High</x:v>
@@ -829,7 +829,7 @@
         <x:v>Retail Deposits and Branch Operations SME lead; data steward; technology owner</x:v>
       </x:c>
       <x:c r="M7" s="79" t="str">
-        <x:v>Named people and approval thresholds require client confirmation.</x:v>
+        <x:v>Confirm Retail operations team (record 2) current-vs-target status, module boundary, volume baseline, and relationship links before this org ownership record is used downstream.</x:v>
       </x:c>
       <x:c r="N7" s="45" t="str">
         <x:v>High</x:v>
@@ -873,7 +873,7 @@
         <x:v>Commercial Lending and Treasury SME lead; data steward; technology owner</x:v>
       </x:c>
       <x:c r="M8" t="str">
-        <x:v>Named people and approval thresholds require client confirmation.</x:v>
+        <x:v>Attach client evidence for Commercial banking leadership (record 3), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="N8" t="str">
         <x:v>High</x:v>
@@ -917,7 +917,7 @@
         <x:v>Cards Operations SME lead; data steward; technology owner</x:v>
       </x:c>
       <x:c r="M9" t="str">
-        <x:v>Named people and approval thresholds require client confirmation.</x:v>
+        <x:v>Reconcile Cards product operations (record 4) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="N9" t="str">
         <x:v>High</x:v>
@@ -961,7 +961,7 @@
         <x:v>Payments Operations SME lead; data steward; technology owner</x:v>
       </x:c>
       <x:c r="M10" t="str">
-        <x:v>Named people and approval thresholds require client confirmation.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Payments operations team (record 5) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="N10" t="str">
         <x:v>Medium</x:v>
@@ -1005,7 +1005,7 @@
         <x:v>Consumer Lending Operations SME lead; data steward; technology owner</x:v>
       </x:c>
       <x:c r="M11" t="str">
-        <x:v>Named people and approval thresholds require client confirmation.</x:v>
+        <x:v>Validate Lending operations team (record 6) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for org ownership.</x:v>
       </x:c>
       <x:c r="N11" t="str">
         <x:v>High</x:v>
@@ -1049,7 +1049,7 @@
         <x:v>Wealth Advisory and Brokerage SME lead; data steward; technology owner</x:v>
       </x:c>
       <x:c r="M12" t="str">
-        <x:v>Named people and approval thresholds require client confirmation.</x:v>
+        <x:v>Confirm Wealth platform team (record 7) current-vs-target status, module boundary, volume baseline, and relationship links before this org ownership record is used downstream.</x:v>
       </x:c>
       <x:c r="N12" t="str">
         <x:v>High</x:v>
@@ -1093,7 +1093,7 @@
         <x:v>Fraud and Risk Operations SME lead; data steward; technology owner</x:v>
       </x:c>
       <x:c r="M13" t="str">
-        <x:v>Named people and approval thresholds require client confirmation.</x:v>
+        <x:v>Validate Fraud operations leadership (record 8) against Fraud Analyst Copilot evidence: model version lineage gaps; confirm feature-store feedback loop owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="N13" t="str">
         <x:v>High</x:v>
@@ -1137,7 +1137,7 @@
         <x:v>Compliance and Model Risk Management SME lead; data steward; technology owner</x:v>
       </x:c>
       <x:c r="M14" t="str">
-        <x:v>Named people and approval thresholds require client confirmation.</x:v>
+        <x:v>Reconcile Compliance risk office (record 9) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="N14" t="str">
         <x:v>High</x:v>
@@ -1181,7 +1181,7 @@
         <x:v>Contact Center and Servicing SME lead; data steward; technology owner</x:v>
       </x:c>
       <x:c r="M15" t="str">
-        <x:v>Named people and approval thresholds require client confirmation.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Customer service operations (record 10) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="N15" t="str">
         <x:v>Medium</x:v>
@@ -1225,7 +1225,7 @@
         <x:v>Digital Account Opening and Onboarding SME lead; data steward; technology owner</x:v>
       </x:c>
       <x:c r="M16" t="str">
-        <x:v>Named people and approval thresholds require client confirmation.</x:v>
+        <x:v>Validate Digital banking product team (record 11) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for org ownership.</x:v>
       </x:c>
       <x:c r="N16" t="str">
         <x:v>High</x:v>
@@ -1269,7 +1269,7 @@
         <x:v>Core Banking Modernization SME lead; data steward; technology owner</x:v>
       </x:c>
       <x:c r="M17" t="str">
-        <x:v>Named people and approval thresholds require client confirmation.</x:v>
+        <x:v>Confirm Core modernization program office (record 12) current-vs-target status, module boundary, volume baseline, and relationship links before this org ownership record is used downstream.</x:v>
       </x:c>
       <x:c r="N17" t="str">
         <x:v>High</x:v>
@@ -1313,7 +1313,7 @@
         <x:v>Customer 360 Data Product SME lead; data steward; technology owner</x:v>
       </x:c>
       <x:c r="M18" t="str">
-        <x:v>Named people and approval thresholds require client confirmation.</x:v>
+        <x:v>Attach client evidence for Customer data product squad (record 13), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="N18" t="str">
         <x:v>High</x:v>
@@ -1357,7 +1357,7 @@
         <x:v>Retail Banking Analytics SME lead; data steward; technology owner</x:v>
       </x:c>
       <x:c r="M19" t="str">
-        <x:v>Named people and approval thresholds require client confirmation.</x:v>
+        <x:v>Reconcile Retail analytics team (record 14) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="N19" t="str">
         <x:v>High</x:v>
@@ -1401,7 +1401,7 @@
         <x:v>Cards Portfolio Analytics SME lead; data steward; technology owner</x:v>
       </x:c>
       <x:c r="M20" t="str">
-        <x:v>Named people and approval thresholds require client confirmation.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Cards analytics team (record 15) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="N20" t="str">
         <x:v>Medium</x:v>
@@ -1445,7 +1445,7 @@
         <x:v>Payments and Settlement Analytics SME lead; data steward; technology owner</x:v>
       </x:c>
       <x:c r="M21" t="str">
-        <x:v>Named people and approval thresholds require client confirmation.</x:v>
+        <x:v>Validate Payments analytics team (record 16) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for org ownership.</x:v>
       </x:c>
       <x:c r="N21" t="str">
         <x:v>High</x:v>
@@ -1489,7 +1489,7 @@
         <x:v>Fraud and Risk Analytics SME lead; data steward; technology owner</x:v>
       </x:c>
       <x:c r="M22" t="str">
-        <x:v>Named people and approval thresholds require client confirmation.</x:v>
+        <x:v>Validate Fraud analytics team (record 17) against Fraud Analyst Copilot evidence: model version lineage gaps; confirm feature-store feedback loop owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="N22" t="str">
         <x:v>High</x:v>
@@ -1533,7 +1533,7 @@
         <x:v>Cloud Data Platform SME lead; data steward; technology owner</x:v>
       </x:c>
       <x:c r="M23" t="str">
-        <x:v>Named people and approval thresholds require client confirmation.</x:v>
+        <x:v>Attach client evidence for Enterprise data platform team (record 18), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="N23" t="str">
         <x:v>High</x:v>
@@ -1577,7 +1577,7 @@
         <x:v>IT Budget and Tower Baseline SME lead; data steward; technology owner</x:v>
       </x:c>
       <x:c r="M24" t="str">
-        <x:v>Named people and approval thresholds require client confirmation.</x:v>
+        <x:v>Reconcile Technology finance office (record 19) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="N24" t="str">
         <x:v>High</x:v>
@@ -1621,7 +1621,7 @@
         <x:v>Vendor and Contract Optimization SME lead; data steward; technology owner</x:v>
       </x:c>
       <x:c r="M25" t="str">
-        <x:v>Named people and approval thresholds require client confirmation.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Vendor management office (record 20) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="N25" t="str">
         <x:v>Medium</x:v>
@@ -1665,7 +1665,7 @@
         <x:v>Infrastructure and CMDB SME lead; data steward; technology owner</x:v>
       </x:c>
       <x:c r="M26" t="str">
-        <x:v>Named people and approval thresholds require client confirmation.</x:v>
+        <x:v>Validate Infrastructure operations team (record 21) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for org ownership.</x:v>
       </x:c>
       <x:c r="N26" t="str">
         <x:v>High</x:v>
@@ -1709,7 +1709,7 @@
         <x:v>Incident Problem Change Operations SME lead; data steward; technology owner</x:v>
       </x:c>
       <x:c r="M27" t="str">
-        <x:v>Named people and approval thresholds require client confirmation.</x:v>
+        <x:v>Confirm IT operations command center (record 22) current-vs-target status, module boundary, volume baseline, and relationship links before this org ownership record is used downstream.</x:v>
       </x:c>
       <x:c r="N27" t="str">
         <x:v>High</x:v>
@@ -1727,7 +1727,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbe7e82c0afe14bc9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R93bfc446164946dd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1802,7 +1802,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ree99f9e875654ec6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7d5498fb53d44f5e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1972,7 +1972,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rab43acd2510d494b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R00da5670db514bb4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2026,7 +2026,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf804deb18cc24abf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc68dc71fc0534294"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2136,7 +2136,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R45ceaf342fa9480f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4cab59525c5241d1"/>
   </x:tableParts>
 </x:worksheet>
 </file>